--- a/HCS-01-QA-Test-Plan.xlsx
+++ b/HCS-01-QA-Test-Plan.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Shows "status": "ok" and "vectors_indexed": 121. If vectors_indexed is 0, the backend has not finished starting — wait and reload.</t>
+          <t>Shows "status": "ok" and "vectors_indexed": 140. If vectors_indexed is 0, the backend has not finished starting — wait and reload.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
